--- a/CHA_Export/input_excel/MUM_AE_CCL_02317_12-25.xlsx
+++ b/CHA_Export/input_excel/MUM_AE_CCL_02317_12-25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yashpal/Documents/Project/XExport/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yashpal/Documents/Project/Xemi_dashboard/CHA_Export/input_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45D4D5B-A75E-3648-9946-C53E492DC458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F1697A-7ACB-6549-8754-4B96329E2CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GENERAL" sheetId="1" r:id="rId1"/>
@@ -415,9 +415,6 @@
     <t>29 Dec 2025</t>
   </si>
   <si>
-    <t>CF</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -1058,6 +1055,9 @@
   </si>
   <si>
     <t>Certificate_Date</t>
+  </si>
+  <si>
+    <t>CIF</t>
   </si>
 </sst>
 </file>
@@ -1774,25 +1774,25 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1" t="s">
         <v>271</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>272</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>273</v>
       </c>
-      <c r="F1" t="s">
-        <v>274</v>
-      </c>
       <c r="G1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
@@ -1803,13 +1803,13 @@
         <v>122</v>
       </c>
       <c r="C2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D2" t="s">
         <v>275</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>276</v>
-      </c>
-      <c r="E2" t="s">
-        <v>277</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
@@ -1829,13 +1829,13 @@
         <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F3" t="s">
         <v>58</v>
@@ -1855,10 +1855,10 @@
         <v>122</v>
       </c>
       <c r="C4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" t="s">
         <v>279</v>
-      </c>
-      <c r="D4" t="s">
-        <v>280</v>
       </c>
       <c r="E4" t="s">
         <v>58</v>
@@ -1881,13 +1881,13 @@
         <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F5" t="s">
         <v>58</v>
@@ -1907,10 +1907,10 @@
         <v>122</v>
       </c>
       <c r="C6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" t="s">
         <v>282</v>
-      </c>
-      <c r="D6" t="s">
-        <v>283</v>
       </c>
       <c r="E6" t="s">
         <v>58</v>
@@ -1933,16 +1933,16 @@
         <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E7" t="s">
         <v>284</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>285</v>
-      </c>
-      <c r="F7" t="s">
-        <v>286</v>
       </c>
       <c r="G7" t="s">
         <v>58</v>
@@ -1956,16 +1956,16 @@
         <v>122</v>
       </c>
       <c r="B8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C8" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" t="s">
         <v>275</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>276</v>
-      </c>
-      <c r="E8" t="s">
-        <v>277</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
@@ -1982,16 +1982,16 @@
         <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
@@ -2008,13 +2008,13 @@
         <v>122</v>
       </c>
       <c r="B10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" t="s">
         <v>279</v>
-      </c>
-      <c r="D10" t="s">
-        <v>280</v>
       </c>
       <c r="E10" t="s">
         <v>58</v>
@@ -2034,16 +2034,16 @@
         <v>122</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F11" t="s">
         <v>58</v>
@@ -2060,13 +2060,13 @@
         <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C12" t="s">
+        <v>281</v>
+      </c>
+      <c r="D12" t="s">
         <v>282</v>
-      </c>
-      <c r="D12" t="s">
-        <v>283</v>
       </c>
       <c r="E12" t="s">
         <v>58</v>
@@ -2086,19 +2086,19 @@
         <v>122</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E13" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" t="s">
         <v>287</v>
-      </c>
-      <c r="F13" t="s">
-        <v>288</v>
       </c>
       <c r="G13" t="s">
         <v>58</v>
@@ -2112,16 +2112,16 @@
         <v>122</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C14" t="s">
+        <v>274</v>
+      </c>
+      <c r="D14" t="s">
         <v>275</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>276</v>
-      </c>
-      <c r="E14" t="s">
-        <v>277</v>
       </c>
       <c r="F14" t="s">
         <v>58</v>
@@ -2138,16 +2138,16 @@
         <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" t="s">
         <v>58</v>
@@ -2164,13 +2164,13 @@
         <v>122</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C16" t="s">
+        <v>278</v>
+      </c>
+      <c r="D16" t="s">
         <v>279</v>
-      </c>
-      <c r="D16" t="s">
-        <v>280</v>
       </c>
       <c r="E16" t="s">
         <v>58</v>
@@ -2190,16 +2190,16 @@
         <v>122</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F17" t="s">
         <v>58</v>
@@ -2216,13 +2216,13 @@
         <v>122</v>
       </c>
       <c r="B18" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C18" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" t="s">
         <v>282</v>
-      </c>
-      <c r="D18" t="s">
-        <v>283</v>
       </c>
       <c r="E18" t="s">
         <v>58</v>
@@ -2242,19 +2242,19 @@
         <v>122</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D19" t="s">
+        <v>283</v>
+      </c>
+      <c r="E19" t="s">
         <v>284</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>285</v>
-      </c>
-      <c r="F19" t="s">
-        <v>286</v>
       </c>
       <c r="G19" t="s">
         <v>58</v>
@@ -2268,16 +2268,16 @@
         <v>122</v>
       </c>
       <c r="B20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
+        <v>274</v>
+      </c>
+      <c r="D20" t="s">
         <v>275</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>276</v>
-      </c>
-      <c r="E20" t="s">
-        <v>277</v>
       </c>
       <c r="F20" t="s">
         <v>58</v>
@@ -2294,16 +2294,16 @@
         <v>122</v>
       </c>
       <c r="B21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F21" t="s">
         <v>58</v>
@@ -2320,13 +2320,13 @@
         <v>122</v>
       </c>
       <c r="B22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C22" t="s">
+        <v>278</v>
+      </c>
+      <c r="D22" t="s">
         <v>279</v>
-      </c>
-      <c r="D22" t="s">
-        <v>280</v>
       </c>
       <c r="E22" t="s">
         <v>58</v>
@@ -2346,16 +2346,16 @@
         <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F23" t="s">
         <v>58</v>
@@ -2372,13 +2372,13 @@
         <v>122</v>
       </c>
       <c r="B24" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D24" t="s">
         <v>282</v>
-      </c>
-      <c r="D24" t="s">
-        <v>283</v>
       </c>
       <c r="E24" t="s">
         <v>58</v>
@@ -2398,19 +2398,19 @@
         <v>122</v>
       </c>
       <c r="B25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E25" t="s">
+        <v>286</v>
+      </c>
+      <c r="F25" t="s">
         <v>287</v>
-      </c>
-      <c r="F25" t="s">
-        <v>288</v>
       </c>
       <c r="G25" t="s">
         <v>58</v>
@@ -2424,16 +2424,16 @@
         <v>122</v>
       </c>
       <c r="B26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C26" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" t="s">
         <v>275</v>
       </c>
-      <c r="D26" t="s">
-        <v>276</v>
-      </c>
       <c r="E26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F26" t="s">
         <v>58</v>
@@ -2450,16 +2450,16 @@
         <v>122</v>
       </c>
       <c r="B27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D27" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E27" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F27" t="s">
         <v>58</v>
@@ -2476,13 +2476,13 @@
         <v>122</v>
       </c>
       <c r="B28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C28" t="s">
+        <v>278</v>
+      </c>
+      <c r="D28" t="s">
         <v>279</v>
-      </c>
-      <c r="D28" t="s">
-        <v>280</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -2502,16 +2502,16 @@
         <v>122</v>
       </c>
       <c r="B29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F29" t="s">
         <v>58</v>
@@ -2528,13 +2528,13 @@
         <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C30" t="s">
+        <v>281</v>
+      </c>
+      <c r="D30" t="s">
         <v>282</v>
-      </c>
-      <c r="D30" t="s">
-        <v>283</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
@@ -2554,19 +2554,19 @@
         <v>122</v>
       </c>
       <c r="B31" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E31" t="s">
+        <v>286</v>
+      </c>
+      <c r="F31" t="s">
         <v>287</v>
-      </c>
-      <c r="F31" t="s">
-        <v>288</v>
       </c>
       <c r="G31" t="s">
         <v>58</v>
@@ -2580,16 +2580,16 @@
         <v>122</v>
       </c>
       <c r="B32" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C32" t="s">
+        <v>274</v>
+      </c>
+      <c r="D32" t="s">
         <v>275</v>
       </c>
-      <c r="D32" t="s">
-        <v>276</v>
-      </c>
       <c r="E32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F32" t="s">
         <v>58</v>
@@ -2606,16 +2606,16 @@
         <v>122</v>
       </c>
       <c r="B33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C33" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D33" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E33" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F33" t="s">
         <v>58</v>
@@ -2632,13 +2632,13 @@
         <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C34" t="s">
+        <v>278</v>
+      </c>
+      <c r="D34" t="s">
         <v>279</v>
-      </c>
-      <c r="D34" t="s">
-        <v>280</v>
       </c>
       <c r="E34" t="s">
         <v>58</v>
@@ -2658,16 +2658,16 @@
         <v>122</v>
       </c>
       <c r="B35" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D35" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F35" t="s">
         <v>58</v>
@@ -2684,13 +2684,13 @@
         <v>122</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" t="s">
         <v>282</v>
-      </c>
-      <c r="D36" t="s">
-        <v>283</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
@@ -2710,19 +2710,19 @@
         <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C37" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E37" t="s">
+        <v>286</v>
+      </c>
+      <c r="F37" t="s">
         <v>287</v>
-      </c>
-      <c r="F37" t="s">
-        <v>288</v>
       </c>
       <c r="G37" t="s">
         <v>58</v>
@@ -2736,16 +2736,16 @@
         <v>122</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C38" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" t="s">
         <v>275</v>
       </c>
-      <c r="D38" t="s">
-        <v>276</v>
-      </c>
       <c r="E38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F38" t="s">
         <v>58</v>
@@ -2762,16 +2762,16 @@
         <v>122</v>
       </c>
       <c r="B39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D39" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F39" t="s">
         <v>58</v>
@@ -2788,13 +2788,13 @@
         <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C40" t="s">
+        <v>278</v>
+      </c>
+      <c r="D40" t="s">
         <v>279</v>
-      </c>
-      <c r="D40" t="s">
-        <v>280</v>
       </c>
       <c r="E40" t="s">
         <v>58</v>
@@ -2814,16 +2814,16 @@
         <v>122</v>
       </c>
       <c r="B41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E41" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
         <v>58</v>
@@ -2840,13 +2840,13 @@
         <v>122</v>
       </c>
       <c r="B42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C42" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" t="s">
         <v>282</v>
-      </c>
-      <c r="D42" t="s">
-        <v>283</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
@@ -2866,19 +2866,19 @@
         <v>122</v>
       </c>
       <c r="B43" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C43" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D43" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E43" t="s">
+        <v>286</v>
+      </c>
+      <c r="F43" t="s">
         <v>287</v>
-      </c>
-      <c r="F43" t="s">
-        <v>288</v>
       </c>
       <c r="G43" t="s">
         <v>58</v>
@@ -2892,16 +2892,16 @@
         <v>122</v>
       </c>
       <c r="B44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C44" t="s">
+        <v>274</v>
+      </c>
+      <c r="D44" t="s">
         <v>275</v>
       </c>
-      <c r="D44" t="s">
-        <v>276</v>
-      </c>
       <c r="E44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F44" t="s">
         <v>58</v>
@@ -2918,16 +2918,16 @@
         <v>122</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D45" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F45" t="s">
         <v>58</v>
@@ -2944,13 +2944,13 @@
         <v>122</v>
       </c>
       <c r="B46" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C46" t="s">
+        <v>278</v>
+      </c>
+      <c r="D46" t="s">
         <v>279</v>
-      </c>
-      <c r="D46" t="s">
-        <v>280</v>
       </c>
       <c r="E46" t="s">
         <v>58</v>
@@ -2970,16 +2970,16 @@
         <v>122</v>
       </c>
       <c r="B47" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C47" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E47" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F47" t="s">
         <v>58</v>
@@ -2996,13 +2996,13 @@
         <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C48" t="s">
+        <v>281</v>
+      </c>
+      <c r="D48" t="s">
         <v>282</v>
-      </c>
-      <c r="D48" t="s">
-        <v>283</v>
       </c>
       <c r="E48" t="s">
         <v>58</v>
@@ -3022,19 +3022,19 @@
         <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C49" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E49" t="s">
+        <v>286</v>
+      </c>
+      <c r="F49" t="s">
         <v>287</v>
-      </c>
-      <c r="F49" t="s">
-        <v>288</v>
       </c>
       <c r="G49" t="s">
         <v>58</v>
@@ -3068,22 +3068,22 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" t="s">
         <v>290</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>291</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>292</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>293</v>
-      </c>
-      <c r="G1" t="s">
-        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -3104,25 +3104,25 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D1" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s">
         <v>295</v>
       </c>
-      <c r="D1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>296</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>297</v>
-      </c>
-      <c r="H1" t="s">
-        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -3143,31 +3143,31 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" t="s">
         <v>299</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>300</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>301</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>302</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>303</v>
       </c>
-      <c r="H1" t="s">
-        <v>304</v>
-      </c>
       <c r="I1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3188,19 +3188,19 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D1" t="s">
         <v>305</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>306</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>307</v>
-      </c>
-      <c r="F1" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3211,10 +3211,10 @@
         <v>122</v>
       </c>
       <c r="C2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D2" t="s">
         <v>309</v>
-      </c>
-      <c r="D2" t="s">
-        <v>310</v>
       </c>
       <c r="E2" t="s">
         <v>58</v>
@@ -3228,13 +3228,13 @@
         <v>122</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C3" t="s">
+        <v>308</v>
+      </c>
+      <c r="D3" t="s">
         <v>309</v>
-      </c>
-      <c r="D3" t="s">
-        <v>310</v>
       </c>
       <c r="E3" t="s">
         <v>58</v>
@@ -3255,51 +3255,62 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1" t="s">
         <v>80</v>
       </c>
       <c r="C1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E1" t="s">
         <v>312</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>313</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>314</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>315</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>316</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>317</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>318</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>319</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>320</v>
-      </c>
-      <c r="M1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B2" t="s">
         <v>122</v>
@@ -3308,13 +3319,13 @@
         <v>51</v>
       </c>
       <c r="D2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E2" t="s">
         <v>123</v>
       </c>
       <c r="F2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G2" t="s">
         <v>124</v>
@@ -3326,21 +3337,21 @@
         <v>50</v>
       </c>
       <c r="J2" t="s">
+        <v>324</v>
+      </c>
+      <c r="K2" t="s">
         <v>325</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
         <v>326</v>
-      </c>
-      <c r="L2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B3" t="s">
         <v>122</v>
@@ -3349,13 +3360,13 @@
         <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E3" t="s">
         <v>123</v>
       </c>
       <c r="F3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G3" t="s">
         <v>124</v>
@@ -3367,21 +3378,21 @@
         <v>50</v>
       </c>
       <c r="J3" t="s">
+        <v>324</v>
+      </c>
+      <c r="K3" t="s">
         <v>325</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" t="s">
         <v>326</v>
-      </c>
-      <c r="L3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B4" t="s">
         <v>122</v>
@@ -3390,13 +3401,13 @@
         <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E4" t="s">
         <v>123</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G4" t="s">
         <v>124</v>
@@ -3408,21 +3419,21 @@
         <v>50</v>
       </c>
       <c r="J4" t="s">
+        <v>324</v>
+      </c>
+      <c r="K4" t="s">
         <v>325</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" t="s">
         <v>326</v>
-      </c>
-      <c r="L4" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B5" t="s">
         <v>122</v>
@@ -3431,13 +3442,13 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E5" t="s">
         <v>123</v>
       </c>
       <c r="F5" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G5" t="s">
         <v>124</v>
@@ -3449,16 +3460,16 @@
         <v>50</v>
       </c>
       <c r="J5" t="s">
+        <v>324</v>
+      </c>
+      <c r="K5" t="s">
         <v>325</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5" t="s">
         <v>326</v>
-      </c>
-      <c r="L5" t="s">
-        <v>58</v>
-      </c>
-      <c r="M5" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -3476,25 +3487,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
         <v>334</v>
       </c>
-      <c r="B1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>335</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>336</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>337</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>338</v>
-      </c>
-      <c r="G1" t="s">
-        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -3584,6 +3595,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AS2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="13" max="13" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -3733,40 +3756,40 @@
         <v>124</v>
       </c>
       <c r="D2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G2" t="s">
         <v>125</v>
       </c>
-      <c r="E2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K2" t="s">
         <v>126</v>
       </c>
-      <c r="H2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N2" t="s">
+        <v>125</v>
+      </c>
+      <c r="O2" t="s">
         <v>127</v>
-      </c>
-      <c r="L2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M2" t="s">
-        <v>58</v>
-      </c>
-      <c r="N2" t="s">
-        <v>126</v>
-      </c>
-      <c r="O2" t="s">
-        <v>128</v>
       </c>
       <c r="P2" t="s">
         <v>58</v>
@@ -3862,7 +3885,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS1 A2:C2 E2:AS2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3877,97 +3900,97 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
         <v>129</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>132</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>133</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>134</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>135</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>136</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>137</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>138</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>139</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>140</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>141</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>142</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>144</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>145</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>146</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>147</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>148</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>149</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>150</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>151</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>152</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>153</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>154</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>155</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>156</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>157</v>
       </c>
       <c r="AE1" t="s">
         <v>120</v>
       </c>
       <c r="AF1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG1" t="s">
         <v>46</v>
@@ -3979,19 +4002,19 @@
         <v>121</v>
       </c>
       <c r="AJ1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AK1" t="s">
         <v>159</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>160</v>
       </c>
       <c r="AL1" t="s">
         <v>113</v>
       </c>
       <c r="AM1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AN1" t="s">
         <v>161</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>162</v>
       </c>
       <c r="AO1" t="s">
         <v>114</v>
@@ -4000,115 +4023,115 @@
         <v>117</v>
       </c>
       <c r="AQ1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AR1" t="s">
         <v>163</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>164</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>165</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>166</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>167</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>168</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>169</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>170</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>171</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>172</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>173</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>174</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>175</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>176</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>177</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>178</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>179</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>180</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>181</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>182</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>183</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>184</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>185</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>186</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>187</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>188</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>189</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>190</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>191</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>192</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>193</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>194</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>195</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>196</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>197</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>198</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:79" x14ac:dyDescent="0.2">
@@ -4119,25 +4142,25 @@
         <v>122</v>
       </c>
       <c r="C2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" t="s">
         <v>200</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>201</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>202</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" t="s">
         <v>203</v>
       </c>
-      <c r="G2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>204</v>
-      </c>
-      <c r="I2" t="s">
-        <v>205</v>
       </c>
       <c r="J2" t="s">
         <v>65</v>
@@ -4146,43 +4169,43 @@
         <v>58</v>
       </c>
       <c r="L2" t="s">
+        <v>205</v>
+      </c>
+      <c r="M2" t="s">
         <v>206</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>207</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>208</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>58</v>
+      </c>
+      <c r="R2" t="s">
+        <v>58</v>
+      </c>
+      <c r="S2" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" t="s">
+        <v>58</v>
+      </c>
+      <c r="U2" t="s">
         <v>209</v>
       </c>
-      <c r="P2" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>58</v>
-      </c>
-      <c r="R2" t="s">
-        <v>58</v>
-      </c>
-      <c r="S2" t="s">
-        <v>58</v>
-      </c>
-      <c r="T2" t="s">
-        <v>58</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
         <v>210</v>
       </c>
-      <c r="V2" t="s">
-        <v>58</v>
-      </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>211</v>
-      </c>
-      <c r="X2" t="s">
-        <v>212</v>
       </c>
       <c r="Y2" t="s">
         <v>51</v>
@@ -4191,7 +4214,7 @@
         <v>58</v>
       </c>
       <c r="AA2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB2" t="s">
         <v>58</v>
@@ -4355,25 +4378,25 @@
         <v>122</v>
       </c>
       <c r="B3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C3" t="s">
         <v>214</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" t="s">
         <v>215</v>
       </c>
-      <c r="D3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" t="s">
         <v>216</v>
-      </c>
-      <c r="G3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H3" t="s">
-        <v>217</v>
       </c>
       <c r="I3">
         <v>1E-4</v>
@@ -4382,43 +4405,43 @@
         <v>58</v>
       </c>
       <c r="L3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M3" t="s">
         <v>206</v>
       </c>
-      <c r="M3" t="s">
-        <v>207</v>
-      </c>
       <c r="N3" t="s">
+        <v>217</v>
+      </c>
+      <c r="O3" t="s">
         <v>218</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" t="s">
+        <v>58</v>
+      </c>
+      <c r="T3" t="s">
+        <v>58</v>
+      </c>
+      <c r="U3" t="s">
         <v>219</v>
       </c>
-      <c r="P3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S3" t="s">
-        <v>58</v>
-      </c>
-      <c r="T3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U3" t="s">
-        <v>220</v>
-      </c>
       <c r="V3" t="s">
         <v>58</v>
       </c>
       <c r="W3" t="s">
+        <v>210</v>
+      </c>
+      <c r="X3" t="s">
         <v>211</v>
-      </c>
-      <c r="X3" t="s">
-        <v>212</v>
       </c>
       <c r="Y3" t="s">
         <v>51</v>
@@ -4427,7 +4450,7 @@
         <v>58</v>
       </c>
       <c r="AA3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AB3" t="s">
         <v>58</v>
@@ -4591,73 +4614,73 @@
         <v>122</v>
       </c>
       <c r="B4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C4" t="s">
         <v>221</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>222</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" t="s">
         <v>223</v>
       </c>
-      <c r="E4" t="s">
-        <v>202</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" t="s">
         <v>224</v>
       </c>
-      <c r="G4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>225</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
+        <v>201</v>
+      </c>
+      <c r="K4" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" t="s">
         <v>226</v>
       </c>
-      <c r="J4" t="s">
-        <v>202</v>
-      </c>
-      <c r="K4" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
+        <v>206</v>
+      </c>
+      <c r="N4" t="s">
+        <v>207</v>
+      </c>
+      <c r="O4" t="s">
+        <v>208</v>
+      </c>
+      <c r="P4" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>58</v>
+      </c>
+      <c r="R4" t="s">
+        <v>58</v>
+      </c>
+      <c r="S4" t="s">
+        <v>58</v>
+      </c>
+      <c r="T4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U4" t="s">
         <v>227</v>
       </c>
-      <c r="M4" t="s">
-        <v>207</v>
-      </c>
-      <c r="N4" t="s">
-        <v>208</v>
-      </c>
-      <c r="O4" t="s">
-        <v>209</v>
-      </c>
-      <c r="P4" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>58</v>
-      </c>
-      <c r="R4" t="s">
-        <v>58</v>
-      </c>
-      <c r="S4" t="s">
-        <v>58</v>
-      </c>
-      <c r="T4" t="s">
-        <v>58</v>
-      </c>
-      <c r="U4" t="s">
-        <v>228</v>
-      </c>
       <c r="V4" t="s">
         <v>58</v>
       </c>
       <c r="W4" t="s">
+        <v>210</v>
+      </c>
+      <c r="X4" t="s">
         <v>211</v>
-      </c>
-      <c r="X4" t="s">
-        <v>212</v>
       </c>
       <c r="Y4" t="s">
         <v>51</v>
@@ -4666,37 +4689,37 @@
         <v>58</v>
       </c>
       <c r="AA4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>229</v>
       </c>
-      <c r="AB4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>58</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>230</v>
-      </c>
       <c r="AK4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL4" t="s">
         <v>58</v>
@@ -4830,25 +4853,25 @@
         <v>122</v>
       </c>
       <c r="B5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" t="s">
         <v>231</v>
       </c>
-      <c r="C5" t="s">
-        <v>232</v>
-      </c>
       <c r="D5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" t="s">
         <v>216</v>
-      </c>
-      <c r="G5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" t="s">
-        <v>217</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -4857,43 +4880,43 @@
         <v>58</v>
       </c>
       <c r="L5" t="s">
+        <v>205</v>
+      </c>
+      <c r="M5" t="s">
         <v>206</v>
       </c>
-      <c r="M5" t="s">
-        <v>207</v>
-      </c>
       <c r="N5" t="s">
+        <v>217</v>
+      </c>
+      <c r="O5" t="s">
         <v>218</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>58</v>
+      </c>
+      <c r="R5" t="s">
+        <v>58</v>
+      </c>
+      <c r="S5" t="s">
+        <v>58</v>
+      </c>
+      <c r="T5" t="s">
+        <v>58</v>
+      </c>
+      <c r="U5" t="s">
         <v>219</v>
       </c>
-      <c r="P5" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" t="s">
-        <v>58</v>
-      </c>
-      <c r="S5" t="s">
-        <v>58</v>
-      </c>
-      <c r="T5" t="s">
-        <v>58</v>
-      </c>
-      <c r="U5" t="s">
-        <v>220</v>
-      </c>
       <c r="V5" t="s">
         <v>58</v>
       </c>
       <c r="W5" t="s">
+        <v>210</v>
+      </c>
+      <c r="X5" t="s">
         <v>211</v>
-      </c>
-      <c r="X5" t="s">
-        <v>212</v>
       </c>
       <c r="Y5" t="s">
         <v>51</v>
@@ -4902,7 +4925,7 @@
         <v>58</v>
       </c>
       <c r="AA5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AB5" t="s">
         <v>58</v>
@@ -5066,25 +5089,25 @@
         <v>122</v>
       </c>
       <c r="B6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C6" t="s">
         <v>233</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>234</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" t="s">
         <v>235</v>
       </c>
-      <c r="E6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" t="s">
         <v>236</v>
-      </c>
-      <c r="G6" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" t="s">
-        <v>237</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -5096,16 +5119,16 @@
         <v>58</v>
       </c>
       <c r="L6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M6" t="s">
         <v>206</v>
       </c>
-      <c r="M6" t="s">
-        <v>207</v>
-      </c>
       <c r="N6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P6" t="s">
         <v>58</v>
@@ -5123,16 +5146,16 @@
         <v>58</v>
       </c>
       <c r="U6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="V6" t="s">
         <v>58</v>
       </c>
       <c r="W6" t="s">
+        <v>210</v>
+      </c>
+      <c r="X6" t="s">
         <v>211</v>
-      </c>
-      <c r="X6" t="s">
-        <v>212</v>
       </c>
       <c r="Y6" t="s">
         <v>51</v>
@@ -5141,7 +5164,7 @@
         <v>58</v>
       </c>
       <c r="AA6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AB6" t="s">
         <v>58</v>
@@ -5305,25 +5328,25 @@
         <v>122</v>
       </c>
       <c r="B7" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" t="s">
-        <v>241</v>
-      </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
+        <v>215</v>
+      </c>
+      <c r="G7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" t="s">
         <v>216</v>
-      </c>
-      <c r="G7" t="s">
-        <v>122</v>
-      </c>
-      <c r="H7" t="s">
-        <v>217</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -5335,43 +5358,43 @@
         <v>58</v>
       </c>
       <c r="L7" t="s">
+        <v>205</v>
+      </c>
+      <c r="M7" t="s">
         <v>206</v>
       </c>
-      <c r="M7" t="s">
-        <v>207</v>
-      </c>
       <c r="N7" t="s">
+        <v>217</v>
+      </c>
+      <c r="O7" t="s">
         <v>218</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" t="s">
+        <v>58</v>
+      </c>
+      <c r="S7" t="s">
+        <v>58</v>
+      </c>
+      <c r="T7" t="s">
+        <v>58</v>
+      </c>
+      <c r="U7" t="s">
         <v>219</v>
       </c>
-      <c r="P7" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>58</v>
-      </c>
-      <c r="R7" t="s">
-        <v>58</v>
-      </c>
-      <c r="S7" t="s">
-        <v>58</v>
-      </c>
-      <c r="T7" t="s">
-        <v>58</v>
-      </c>
-      <c r="U7" t="s">
-        <v>220</v>
-      </c>
       <c r="V7" t="s">
         <v>58</v>
       </c>
       <c r="W7" t="s">
+        <v>210</v>
+      </c>
+      <c r="X7" t="s">
         <v>211</v>
-      </c>
-      <c r="X7" t="s">
-        <v>212</v>
       </c>
       <c r="Y7" t="s">
         <v>51</v>
@@ -5380,7 +5403,7 @@
         <v>58</v>
       </c>
       <c r="AA7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AB7" t="s">
         <v>58</v>
@@ -5544,25 +5567,25 @@
         <v>122</v>
       </c>
       <c r="B8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" t="s">
         <v>242</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>243</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F8" t="s">
         <v>244</v>
       </c>
-      <c r="E8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" t="s">
         <v>245</v>
-      </c>
-      <c r="G8" t="s">
-        <v>122</v>
-      </c>
-      <c r="H8" t="s">
-        <v>246</v>
       </c>
       <c r="I8">
         <v>38</v>
@@ -5574,16 +5597,16 @@
         <v>58</v>
       </c>
       <c r="L8" t="s">
+        <v>205</v>
+      </c>
+      <c r="M8" t="s">
         <v>206</v>
       </c>
-      <c r="M8" t="s">
-        <v>207</v>
-      </c>
       <c r="N8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P8" t="s">
         <v>58</v>
@@ -5601,16 +5624,16 @@
         <v>58</v>
       </c>
       <c r="U8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="V8" t="s">
         <v>58</v>
       </c>
       <c r="W8" t="s">
+        <v>210</v>
+      </c>
+      <c r="X8" t="s">
         <v>211</v>
-      </c>
-      <c r="X8" t="s">
-        <v>212</v>
       </c>
       <c r="Y8" t="s">
         <v>51</v>
@@ -5619,7 +5642,7 @@
         <v>58</v>
       </c>
       <c r="AA8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AB8" t="s">
         <v>58</v>
@@ -5783,25 +5806,25 @@
         <v>122</v>
       </c>
       <c r="B9" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" t="s">
         <v>249</v>
       </c>
-      <c r="C9" t="s">
-        <v>250</v>
-      </c>
       <c r="D9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
+        <v>215</v>
+      </c>
+      <c r="G9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" t="s">
         <v>216</v>
-      </c>
-      <c r="G9" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" t="s">
-        <v>217</v>
       </c>
       <c r="I9">
         <v>1E-4</v>
@@ -5813,43 +5836,43 @@
         <v>58</v>
       </c>
       <c r="L9" t="s">
+        <v>205</v>
+      </c>
+      <c r="M9" t="s">
         <v>206</v>
       </c>
-      <c r="M9" t="s">
-        <v>207</v>
-      </c>
       <c r="N9" t="s">
+        <v>217</v>
+      </c>
+      <c r="O9" t="s">
         <v>218</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>58</v>
+      </c>
+      <c r="R9" t="s">
+        <v>58</v>
+      </c>
+      <c r="S9" t="s">
+        <v>58</v>
+      </c>
+      <c r="T9" t="s">
+        <v>58</v>
+      </c>
+      <c r="U9" t="s">
         <v>219</v>
       </c>
-      <c r="P9" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>58</v>
-      </c>
-      <c r="R9" t="s">
-        <v>58</v>
-      </c>
-      <c r="S9" t="s">
-        <v>58</v>
-      </c>
-      <c r="T9" t="s">
-        <v>58</v>
-      </c>
-      <c r="U9" t="s">
-        <v>220</v>
-      </c>
       <c r="V9" t="s">
         <v>58</v>
       </c>
       <c r="W9" t="s">
+        <v>210</v>
+      </c>
+      <c r="X9" t="s">
         <v>211</v>
-      </c>
-      <c r="X9" t="s">
-        <v>212</v>
       </c>
       <c r="Y9" t="s">
         <v>51</v>
@@ -5858,7 +5881,7 @@
         <v>58</v>
       </c>
       <c r="AA9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AB9" t="s">
         <v>58</v>
@@ -6035,43 +6058,43 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" t="s">
         <v>251</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>252</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>253</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>254</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>255</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>256</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>257</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>258</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>259</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>260</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>261</v>
-      </c>
-      <c r="N1" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -6092,43 +6115,43 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" t="s">
         <v>251</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>252</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>253</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>254</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>255</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>256</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>257</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>258</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>259</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>260</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>261</v>
-      </c>
-      <c r="N1" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -6149,43 +6172,43 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" t="s">
         <v>251</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>252</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>253</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>254</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>255</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>256</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>257</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>258</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>259</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>260</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>261</v>
-      </c>
-      <c r="N1" t="s">
-        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -6206,34 +6229,34 @@
         <v>80</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" t="s">
         <v>263</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>264</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>265</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>266</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>267</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>268</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>269</v>
       </c>
-      <c r="J1" t="s">
-        <v>270</v>
-      </c>
       <c r="K1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
